--- a/diseases/d169/2010-2014.xlsx
+++ b/diseases/d169/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -1357,9 +1354,6 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -1653,9 +1647,6 @@
       <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.0082018756356774</v>
       </c>
@@ -2097,9 +2088,6 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -2541,9 +2529,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -2985,9 +2970,6 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -3429,9 +3411,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -3873,9 +3852,6 @@
       <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -4317,9 +4293,6 @@
       <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -4761,9 +4734,6 @@
       <c r="O29" t="n">
         <v>7</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01435328236243545</v>
       </c>
@@ -5205,9 +5175,6 @@
       <c r="O32" t="n">
         <v>23</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.04716078490514505</v>
       </c>
@@ -5649,9 +5616,6 @@
       <c r="O35" t="n">
         <v>5</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.01025234454459675</v>
       </c>
@@ -6093,9 +6057,6 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -6537,9 +6498,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6981,9 +6939,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7425,9 +7380,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7869,9 +7821,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -8313,9 +8262,6 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -8757,9 +8703,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -9053,9 +8996,6 @@
       <c r="O58" t="n">
         <v>4</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.008142055500789488</v>
       </c>
@@ -9497,9 +9437,6 @@
       <c r="O61" t="n">
         <v>3</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.006106541625592117</v>
       </c>
@@ -9941,9 +9878,6 @@
       <c r="O64" t="n">
         <v>5</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.01017756937598686</v>
       </c>
@@ -10385,9 +10319,6 @@
       <c r="O67" t="n">
         <v>4</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.008142055500789488</v>
       </c>
@@ -10829,9 +10760,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -11125,9 +11053,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -11569,9 +11494,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12013,9 +11935,6 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -12309,9 +12228,6 @@
       <c r="O80" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -12753,9 +12669,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -13197,9 +13110,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -13641,9 +13551,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -14085,9 +13992,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -14529,9 +14433,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -14973,9 +14874,6 @@
       <c r="O98" t="n">
         <v>12</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.02419375349744648</v>
       </c>
@@ -15417,9 +15315,6 @@
       <c r="O101" t="n">
         <v>15</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.03024219187180811</v>
       </c>
@@ -15861,9 +15756,6 @@
       <c r="O104" t="n">
         <v>5</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.01008073062393603</v>
       </c>
@@ -16305,9 +16197,6 @@
       <c r="O107" t="n">
         <v>2</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -16749,9 +16638,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -17045,9 +16931,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -17489,9 +17372,6 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -17933,9 +17813,6 @@
       <c r="O118" t="n">
         <v>2</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -18377,9 +18254,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -18821,9 +18695,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -19265,9 +19136,6 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -19709,9 +19577,6 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -20153,9 +20018,6 @@
       <c r="O133" t="n">
         <v>3</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.005991472397251715</v>
       </c>
@@ -20449,9 +20311,6 @@
       <c r="O135" t="n">
         <v>4</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.007988629863002287</v>
       </c>
@@ -20745,9 +20604,6 @@
       <c r="O137" t="n">
         <v>2</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -21189,9 +21045,6 @@
       <c r="O140" t="n">
         <v>2</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -21485,9 +21338,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -21929,9 +21779,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -22373,9 +22220,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -22817,9 +22661,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -23261,9 +23102,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -23557,9 +23395,6 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -24001,9 +23836,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -24445,9 +24277,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -24889,9 +24718,6 @@
       <c r="O165" t="n">
         <v>4</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.007914671060680983</v>
       </c>
@@ -25333,9 +25159,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -25775,9 +25598,6 @@
         <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
